--- a/Financial Analysis/AMBQ.xlsx
+++ b/Financial Analysis/AMBQ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C78AC463-2BB1-4D9C-A2B8-45E492235D83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9C7DCD6-F19B-4B37-9F44-C6D65F0FB319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{752363E1-E984-4A0D-A60C-623CC0252B9A}"/>
   </bookViews>
@@ -172,7 +172,7 @@
     <t>Consensus</t>
   </si>
   <si>
-    <t>Overvalued</t>
+    <t>Heavily overvalued</t>
   </si>
 </sst>
 </file>
@@ -182,7 +182,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$$-409]#,##0.00"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -208,15 +208,6 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -259,8 +250,8 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -655,17 +646,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="2">
-        <v>35.03</v>
+        <v>25.87</v>
       </c>
       <c r="E3" s="5">
-        <v>45905</v>
+        <v>45975</v>
       </c>
       <c r="F3" s="5">
         <f ca="1">TODAY()</f>
-        <v>45905</v>
+        <v>45975</v>
       </c>
       <c r="G3" s="5">
-        <v>45994</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -673,11 +664,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="3">
-        <f>18.2</f>
-        <v>18.2</v>
+        <f>18.3</f>
+        <v>18.3</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -686,7 +677,7 @@
       </c>
       <c r="D5" s="3">
         <f>D3*D4</f>
-        <v>637.54600000000005</v>
+        <v>473.42100000000005</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -694,11 +685,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="3">
-        <f>47.5</f>
-        <v>47.5</v>
+        <f>146.5</f>
+        <v>146.5</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -709,7 +700,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -718,7 +709,7 @@
       </c>
       <c r="D8" s="3">
         <f>D6-D7</f>
-        <v>47.5</v>
+        <v>146.5</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -727,7 +718,7 @@
       </c>
       <c r="D9" s="3">
         <f>D5-D8</f>
-        <v>590.04600000000005</v>
+        <v>326.92100000000005</v>
       </c>
     </row>
   </sheetData>
@@ -820,11 +811,12 @@
       <c r="D3" s="8">
         <v>20.3</v>
       </c>
-      <c r="E3" s="10">
-        <v>19</v>
-      </c>
-      <c r="F3" s="10">
-        <v>25</v>
+      <c r="E3" s="8">
+        <v>20.3</v>
+      </c>
+      <c r="F3" s="8">
+        <f>M3-E3-D3-C3</f>
+        <v>20.3</v>
       </c>
       <c r="G3" s="8">
         <v>15.7</v>
@@ -832,8 +824,8 @@
       <c r="H3" s="8">
         <v>17.899999999999999</v>
       </c>
-      <c r="I3" s="1">
-        <v>18</v>
+      <c r="I3" s="8">
+        <v>18.2</v>
       </c>
       <c r="J3" s="1">
         <v>19</v>
@@ -846,7 +838,7 @@
       </c>
       <c r="N3" s="8">
         <f>SUM(G3:J3)</f>
-        <v>70.599999999999994</v>
+        <v>70.8</v>
       </c>
       <c r="O3" s="8">
         <v>82</v>
@@ -898,62 +890,75 @@
       <c r="D4" s="3">
         <v>13.8</v>
       </c>
-      <c r="F4" s="3"/>
+      <c r="E4" s="3">
+        <v>13.7</v>
+      </c>
+      <c r="F4" s="11">
+        <f>M4-E4-D4-C4</f>
+        <v>15.299999999999994</v>
+      </c>
       <c r="G4" s="3">
         <v>7.3</v>
       </c>
       <c r="H4" s="3">
         <v>10.7</v>
       </c>
+      <c r="I4" s="3">
+        <v>10.5</v>
+      </c>
+      <c r="J4">
+        <f>J3-J5</f>
+        <v>10.83</v>
+      </c>
       <c r="L4" s="3">
         <v>46.1</v>
       </c>
       <c r="M4" s="3">
         <v>51.8</v>
       </c>
-      <c r="N4" s="3">
-        <f>N3-N5</f>
-        <v>32.475999999999992</v>
+      <c r="N4" s="11">
+        <f>SUM(G4:J4)</f>
+        <v>39.33</v>
       </c>
       <c r="O4" s="3">
         <f t="shared" ref="O4:X4" si="1">O3-O5</f>
-        <v>37.72</v>
+        <v>47.56</v>
       </c>
       <c r="P4" s="3">
         <f t="shared" si="1"/>
-        <v>64.123999999999995</v>
+        <v>79.457999999999998</v>
       </c>
       <c r="Q4" s="3">
         <f t="shared" si="1"/>
-        <v>102.5984</v>
+        <v>124.90240000000001</v>
       </c>
       <c r="R4" s="3">
         <f t="shared" si="1"/>
-        <v>153.89760000000001</v>
+        <v>187.35360000000003</v>
       </c>
       <c r="S4" s="3">
         <f t="shared" si="1"/>
-        <v>215.45664000000002</v>
+        <v>262.29504000000003</v>
       </c>
       <c r="T4" s="3">
         <f t="shared" si="1"/>
-        <v>280.09363200000001</v>
+        <v>340.98355200000003</v>
       </c>
       <c r="U4" s="3">
         <f t="shared" si="1"/>
-        <v>336.11235840000001</v>
+        <v>409.18026240000006</v>
       </c>
       <c r="V4" s="3">
         <f t="shared" si="1"/>
-        <v>369.72359424000007</v>
+        <v>450.09828864000013</v>
       </c>
       <c r="W4" s="3">
         <f t="shared" si="1"/>
-        <v>388.20977395200009</v>
+        <v>472.60320307200016</v>
       </c>
       <c r="X4" s="3">
         <f t="shared" si="1"/>
-        <v>407.62026264960014</v>
+        <v>496.23336322560016</v>
       </c>
     </row>
     <row r="5" spans="2:140" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -968,6 +973,14 @@
         <f>D3-D4</f>
         <v>6.5</v>
       </c>
+      <c r="E5" s="8">
+        <f>E3-E4</f>
+        <v>6.6000000000000014</v>
+      </c>
+      <c r="F5" s="8">
+        <f>F3-F4</f>
+        <v>5.0000000000000071</v>
+      </c>
       <c r="G5" s="8">
         <f>G3-G4</f>
         <v>8.3999999999999986</v>
@@ -976,6 +989,14 @@
         <f>H3-H4</f>
         <v>7.1999999999999993</v>
       </c>
+      <c r="I5" s="8">
+        <f>I3-I4</f>
+        <v>7.6999999999999993</v>
+      </c>
+      <c r="J5" s="1">
+        <f>J3*0.43</f>
+        <v>8.17</v>
+      </c>
       <c r="L5" s="8">
         <f>L3-L4</f>
         <v>19.399999999999999</v>
@@ -985,48 +1006,48 @@
         <v>24.299999999999997</v>
       </c>
       <c r="N5" s="8">
-        <f>N3*0.54</f>
-        <v>38.124000000000002</v>
+        <f>N3-N4</f>
+        <v>31.47</v>
       </c>
       <c r="O5" s="8">
-        <f t="shared" ref="O5:X5" si="2">O3*0.54</f>
-        <v>44.28</v>
+        <f>O3*0.42</f>
+        <v>34.44</v>
       </c>
       <c r="P5" s="8">
-        <f t="shared" si="2"/>
-        <v>75.27600000000001</v>
+        <f>P3*0.43</f>
+        <v>59.942</v>
       </c>
       <c r="Q5" s="8">
-        <f t="shared" si="2"/>
-        <v>120.44160000000002</v>
+        <f>Q3*0.44</f>
+        <v>98.137600000000006</v>
       </c>
       <c r="R5" s="8">
-        <f t="shared" si="2"/>
-        <v>180.66240000000005</v>
+        <f t="shared" ref="R5:X5" si="2">R3*0.44</f>
+        <v>147.20640000000003</v>
       </c>
       <c r="S5" s="8">
         <f t="shared" si="2"/>
-        <v>252.92736000000005</v>
+        <v>206.08896000000004</v>
       </c>
       <c r="T5" s="8">
         <f t="shared" si="2"/>
-        <v>328.80556800000005</v>
+        <v>267.91564800000003</v>
       </c>
       <c r="U5" s="8">
         <f t="shared" si="2"/>
-        <v>394.56668160000009</v>
+        <v>321.49877760000004</v>
       </c>
       <c r="V5" s="8">
         <f t="shared" si="2"/>
-        <v>434.02334976000014</v>
+        <v>353.64865536000008</v>
       </c>
       <c r="W5" s="8">
         <f t="shared" si="2"/>
-        <v>455.72451724800021</v>
+        <v>371.33108812800015</v>
       </c>
       <c r="X5" s="8">
         <f t="shared" si="2"/>
-        <v>478.5107431104002</v>
+        <v>389.89764253440018</v>
       </c>
     </row>
     <row r="6" spans="2:140" x14ac:dyDescent="0.3">
@@ -1039,60 +1060,74 @@
       <c r="D6" s="3">
         <v>9.4</v>
       </c>
+      <c r="E6" s="3">
+        <v>9.6</v>
+      </c>
+      <c r="F6" s="11">
+        <f t="shared" ref="F6:F7" si="3">M6-E6-D6-C6</f>
+        <v>8.8000000000000025</v>
+      </c>
       <c r="G6" s="3">
         <v>8.6999999999999993</v>
       </c>
       <c r="H6" s="3">
         <v>8.9</v>
       </c>
+      <c r="I6" s="3">
+        <v>8.9</v>
+      </c>
+      <c r="J6" s="3">
+        <v>9.1</v>
+      </c>
       <c r="L6" s="3">
         <v>44</v>
       </c>
       <c r="M6" s="3">
         <v>37.200000000000003</v>
       </c>
-      <c r="N6" s="3">
-        <v>36</v>
+      <c r="N6" s="11">
+        <f t="shared" ref="N6:N7" si="4">SUM(G6:J6)</f>
+        <v>35.6</v>
       </c>
       <c r="O6" s="3">
         <f>N6*0.95</f>
-        <v>34.199999999999996</v>
+        <v>33.82</v>
       </c>
       <c r="P6" s="3">
-        <f t="shared" ref="P6:T6" si="3">O6*1.25</f>
-        <v>42.749999999999993</v>
+        <f t="shared" ref="P6:T6" si="5">O6*1.25</f>
+        <v>42.274999999999999</v>
       </c>
       <c r="Q6" s="3">
-        <f t="shared" si="3"/>
-        <v>53.437499999999993</v>
+        <f t="shared" si="5"/>
+        <v>52.84375</v>
       </c>
       <c r="R6" s="3">
-        <f t="shared" si="3"/>
-        <v>66.796874999999986</v>
+        <f t="shared" si="5"/>
+        <v>66.0546875</v>
       </c>
       <c r="S6" s="3">
-        <f t="shared" si="3"/>
-        <v>83.496093749999986</v>
+        <f t="shared" si="5"/>
+        <v>82.568359375</v>
       </c>
       <c r="T6" s="3">
-        <f t="shared" si="3"/>
-        <v>104.37011718749999</v>
+        <f t="shared" si="5"/>
+        <v>103.21044921875</v>
       </c>
       <c r="U6" s="3">
         <f>T6*1.2</f>
-        <v>125.24414062499997</v>
+        <v>123.8525390625</v>
       </c>
       <c r="V6" s="3">
         <f>U6*1.15</f>
-        <v>144.03076171874994</v>
+        <v>142.430419921875</v>
       </c>
       <c r="W6" s="3">
         <f>V6*1.1</f>
-        <v>158.43383789062494</v>
+        <v>156.6734619140625</v>
       </c>
       <c r="X6" s="3">
         <f>W6*1.05</f>
-        <v>166.35552978515619</v>
+        <v>164.50713500976562</v>
       </c>
     </row>
     <row r="7" spans="2:140" x14ac:dyDescent="0.3">
@@ -1105,61 +1140,74 @@
       <c r="D7" s="3">
         <v>8</v>
       </c>
+      <c r="E7" s="3">
+        <v>7.1</v>
+      </c>
+      <c r="F7" s="11">
+        <f t="shared" si="3"/>
+        <v>6.6000000000000014</v>
+      </c>
       <c r="G7" s="3">
         <v>8.4</v>
       </c>
       <c r="H7" s="3">
         <v>7.1</v>
       </c>
+      <c r="I7" s="3">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="J7" s="3">
+        <v>9.5</v>
+      </c>
       <c r="L7" s="3">
         <v>26.7</v>
       </c>
       <c r="M7" s="3">
         <v>27.7</v>
       </c>
-      <c r="N7" s="3">
-        <f>M7*1.15</f>
-        <v>31.854999999999997</v>
+      <c r="N7" s="11">
+        <f t="shared" si="4"/>
+        <v>33.799999999999997</v>
       </c>
       <c r="O7" s="3">
         <f>N7*0.85</f>
-        <v>27.076749999999997</v>
+        <v>28.729999999999997</v>
       </c>
       <c r="P7" s="3">
         <f>O7*1.6</f>
-        <v>43.322800000000001</v>
+        <v>45.967999999999996</v>
       </c>
       <c r="Q7" s="3">
         <f>P7*1.5</f>
-        <v>64.984200000000001</v>
+        <v>68.951999999999998</v>
       </c>
       <c r="R7" s="3">
         <f>Q7*1.4</f>
-        <v>90.977879999999999</v>
+        <v>96.532799999999995</v>
       </c>
       <c r="S7" s="3">
         <f>R7*1.3</f>
-        <v>118.271244</v>
+        <v>125.49263999999999</v>
       </c>
       <c r="T7" s="3">
         <f>S7*1.2</f>
-        <v>141.9254928</v>
+        <v>150.59116799999998</v>
       </c>
       <c r="U7" s="3">
         <f>T7*1.1</f>
-        <v>156.11804208000001</v>
+        <v>165.65028479999998</v>
       </c>
       <c r="V7" s="3">
         <f>U7*1.05</f>
-        <v>163.92394418400002</v>
+        <v>173.93279903999999</v>
       </c>
       <c r="W7" s="3">
-        <f t="shared" ref="W7:X7" si="4">V7*1.05</f>
-        <v>172.12014139320004</v>
+        <f t="shared" ref="W7:X7" si="6">V7*1.05</f>
+        <v>182.62943899199999</v>
       </c>
       <c r="X7" s="3">
-        <f t="shared" si="4"/>
-        <v>180.72614846286007</v>
+        <f t="shared" si="6"/>
+        <v>191.7609109416</v>
       </c>
     </row>
     <row r="8" spans="2:140" x14ac:dyDescent="0.3">
@@ -1174,6 +1222,14 @@
         <f>SUM(D6:D7)</f>
         <v>17.399999999999999</v>
       </c>
+      <c r="E8" s="3">
+        <f>SUM(E6:E7)</f>
+        <v>16.7</v>
+      </c>
+      <c r="F8" s="3">
+        <f>SUM(F6:F7)</f>
+        <v>15.400000000000004</v>
+      </c>
       <c r="G8" s="3">
         <f>SUM(G6:G7)</f>
         <v>17.100000000000001</v>
@@ -1182,6 +1238,14 @@
         <f>SUM(H6:H7)</f>
         <v>16</v>
       </c>
+      <c r="I8" s="3">
+        <f>SUM(I6:I7)</f>
+        <v>17.700000000000003</v>
+      </c>
+      <c r="J8" s="3">
+        <f>SUM(J6:J7)</f>
+        <v>18.600000000000001</v>
+      </c>
       <c r="L8" s="3">
         <f>SUM(L6:L7)</f>
         <v>70.7</v>
@@ -1191,48 +1255,48 @@
         <v>64.900000000000006</v>
       </c>
       <c r="N8" s="3">
-        <f t="shared" ref="N8:X8" si="5">SUM(N6:N7)</f>
-        <v>67.85499999999999</v>
+        <f t="shared" ref="N8:X8" si="7">SUM(N6:N7)</f>
+        <v>69.400000000000006</v>
       </c>
       <c r="O8" s="3">
-        <f t="shared" si="5"/>
-        <v>61.276749999999993</v>
+        <f t="shared" si="7"/>
+        <v>62.55</v>
       </c>
       <c r="P8" s="3">
-        <f t="shared" si="5"/>
-        <v>86.072800000000001</v>
+        <f t="shared" si="7"/>
+        <v>88.242999999999995</v>
       </c>
       <c r="Q8" s="3">
-        <f t="shared" si="5"/>
-        <v>118.42169999999999</v>
+        <f t="shared" si="7"/>
+        <v>121.79575</v>
       </c>
       <c r="R8" s="3">
-        <f t="shared" si="5"/>
-        <v>157.77475499999997</v>
+        <f t="shared" si="7"/>
+        <v>162.58748750000001</v>
       </c>
       <c r="S8" s="3">
-        <f t="shared" si="5"/>
-        <v>201.76733774999997</v>
+        <f t="shared" si="7"/>
+        <v>208.06099937499999</v>
       </c>
       <c r="T8" s="3">
-        <f t="shared" si="5"/>
-        <v>246.29560998749997</v>
+        <f t="shared" si="7"/>
+        <v>253.80161721874998</v>
       </c>
       <c r="U8" s="3">
-        <f t="shared" si="5"/>
-        <v>281.36218270500001</v>
+        <f t="shared" si="7"/>
+        <v>289.50282386250001</v>
       </c>
       <c r="V8" s="3">
-        <f t="shared" si="5"/>
-        <v>307.95470590274999</v>
+        <f t="shared" si="7"/>
+        <v>316.36321896187496</v>
       </c>
       <c r="W8" s="3">
-        <f t="shared" si="5"/>
-        <v>330.55397928382502</v>
+        <f t="shared" si="7"/>
+        <v>339.30290090606252</v>
       </c>
       <c r="X8" s="3">
-        <f t="shared" si="5"/>
-        <v>347.08167824801626</v>
+        <f t="shared" si="7"/>
+        <v>356.26804595136559</v>
       </c>
     </row>
     <row r="9" spans="2:140" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1247,6 +1311,14 @@
         <f>D5-D8</f>
         <v>-10.899999999999999</v>
       </c>
+      <c r="E9" s="8">
+        <f>E5-E8</f>
+        <v>-10.099999999999998</v>
+      </c>
+      <c r="F9" s="8">
+        <f>F5-F8</f>
+        <v>-10.399999999999997</v>
+      </c>
       <c r="G9" s="8">
         <f>G5-G8</f>
         <v>-8.7000000000000028</v>
@@ -1255,6 +1327,14 @@
         <f>H5-H8</f>
         <v>-8.8000000000000007</v>
       </c>
+      <c r="I9" s="8">
+        <f>I5-I8</f>
+        <v>-10.000000000000004</v>
+      </c>
+      <c r="J9" s="8">
+        <f>J5-J8</f>
+        <v>-10.430000000000001</v>
+      </c>
       <c r="L9" s="8">
         <f>L5-L8</f>
         <v>-51.300000000000004</v>
@@ -1264,48 +1344,48 @@
         <v>-40.600000000000009</v>
       </c>
       <c r="N9" s="8">
-        <f t="shared" ref="N9:X9" si="6">N5-N8</f>
-        <v>-29.730999999999987</v>
+        <f t="shared" ref="N9:X9" si="8">N5-N8</f>
+        <v>-37.930000000000007</v>
       </c>
       <c r="O9" s="8">
-        <f t="shared" si="6"/>
-        <v>-16.996749999999992</v>
+        <f t="shared" si="8"/>
+        <v>-28.11</v>
       </c>
       <c r="P9" s="8">
-        <f t="shared" si="6"/>
-        <v>-10.79679999999999</v>
+        <f t="shared" si="8"/>
+        <v>-28.300999999999995</v>
       </c>
       <c r="Q9" s="8">
-        <f t="shared" si="6"/>
-        <v>2.0199000000000353</v>
+        <f t="shared" si="8"/>
+        <v>-23.658149999999992</v>
       </c>
       <c r="R9" s="8">
-        <f t="shared" si="6"/>
-        <v>22.887645000000077</v>
+        <f t="shared" si="8"/>
+        <v>-15.381087499999978</v>
       </c>
       <c r="S9" s="8">
-        <f t="shared" si="6"/>
-        <v>51.160022250000083</v>
+        <f t="shared" si="8"/>
+        <v>-1.9720393749999516</v>
       </c>
       <c r="T9" s="8">
-        <f t="shared" si="6"/>
-        <v>82.509958012500078</v>
+        <f t="shared" si="8"/>
+        <v>14.114030781250051</v>
       </c>
       <c r="U9" s="8">
-        <f t="shared" si="6"/>
-        <v>113.20449889500009</v>
+        <f t="shared" si="8"/>
+        <v>31.995953737500031</v>
       </c>
       <c r="V9" s="8">
-        <f t="shared" si="6"/>
-        <v>126.06864385725015</v>
+        <f t="shared" si="8"/>
+        <v>37.285436398125114</v>
       </c>
       <c r="W9" s="8">
-        <f t="shared" si="6"/>
-        <v>125.1705379641752</v>
+        <f t="shared" si="8"/>
+        <v>32.028187221937628</v>
       </c>
       <c r="X9" s="8">
-        <f t="shared" si="6"/>
-        <v>131.42906486238394</v>
+        <f t="shared" si="8"/>
+        <v>33.629596583034584</v>
       </c>
     </row>
     <row r="10" spans="2:140" x14ac:dyDescent="0.3">
@@ -1318,20 +1398,34 @@
       <c r="D10" s="3">
         <v>-0.3</v>
       </c>
+      <c r="E10" s="3">
+        <v>-0.7</v>
+      </c>
+      <c r="F10" s="11">
+        <f>M10-E10-D10-C10</f>
+        <v>-0.20000000000000007</v>
+      </c>
       <c r="G10" s="3">
         <v>-0.5</v>
       </c>
       <c r="H10" s="3">
         <v>-0.3</v>
       </c>
+      <c r="I10" s="3">
+        <v>-1</v>
+      </c>
+      <c r="J10" s="3">
+        <v>-1</v>
+      </c>
       <c r="L10" s="3">
         <v>-1</v>
       </c>
       <c r="M10" s="3">
         <v>-1</v>
       </c>
-      <c r="N10" s="3">
-        <v>0</v>
+      <c r="N10" s="11">
+        <f>SUM(G10:J10)</f>
+        <v>-2.8</v>
       </c>
       <c r="O10" s="3">
         <v>0</v>
@@ -1376,6 +1470,14 @@
         <f>D9-D10</f>
         <v>-10.599999999999998</v>
       </c>
+      <c r="E11" s="8">
+        <f>E9-E10</f>
+        <v>-9.3999999999999986</v>
+      </c>
+      <c r="F11" s="8">
+        <f>F9-F10</f>
+        <v>-10.199999999999998</v>
+      </c>
       <c r="G11" s="8">
         <f>G9-G10</f>
         <v>-8.2000000000000028</v>
@@ -1384,6 +1486,14 @@
         <f>H9-H10</f>
         <v>-8.5</v>
       </c>
+      <c r="I11" s="8">
+        <f>I9-I10</f>
+        <v>-9.0000000000000036</v>
+      </c>
+      <c r="J11" s="8">
+        <f>J9-J10</f>
+        <v>-9.4300000000000015</v>
+      </c>
       <c r="L11" s="8">
         <f>L9-L10</f>
         <v>-50.300000000000004</v>
@@ -1394,47 +1504,47 @@
       </c>
       <c r="N11" s="8">
         <f>N9-N10</f>
-        <v>-29.730999999999987</v>
+        <v>-35.13000000000001</v>
       </c>
       <c r="O11" s="8">
-        <f t="shared" ref="O11:X11" si="7">O9-O10</f>
-        <v>-16.996749999999992</v>
+        <f t="shared" ref="O11:X11" si="9">O9-O10</f>
+        <v>-28.11</v>
       </c>
       <c r="P11" s="8">
-        <f t="shared" si="7"/>
-        <v>-10.79679999999999</v>
+        <f t="shared" si="9"/>
+        <v>-28.300999999999995</v>
       </c>
       <c r="Q11" s="8">
-        <f t="shared" si="7"/>
-        <v>2.0199000000000353</v>
+        <f t="shared" si="9"/>
+        <v>-23.658149999999992</v>
       </c>
       <c r="R11" s="8">
-        <f t="shared" si="7"/>
-        <v>22.887645000000077</v>
+        <f t="shared" si="9"/>
+        <v>-15.381087499999978</v>
       </c>
       <c r="S11" s="8">
-        <f t="shared" si="7"/>
-        <v>51.160022250000083</v>
+        <f t="shared" si="9"/>
+        <v>-1.9720393749999516</v>
       </c>
       <c r="T11" s="8">
-        <f t="shared" si="7"/>
-        <v>82.509958012500078</v>
+        <f t="shared" si="9"/>
+        <v>14.114030781250051</v>
       </c>
       <c r="U11" s="8">
-        <f t="shared" si="7"/>
-        <v>113.20449889500009</v>
+        <f t="shared" si="9"/>
+        <v>31.995953737500031</v>
       </c>
       <c r="V11" s="8">
-        <f t="shared" si="7"/>
-        <v>126.06864385725015</v>
+        <f t="shared" si="9"/>
+        <v>37.285436398125114</v>
       </c>
       <c r="W11" s="8">
-        <f t="shared" si="7"/>
-        <v>125.1705379641752</v>
+        <f t="shared" si="9"/>
+        <v>32.028187221937628</v>
       </c>
       <c r="X11" s="8">
-        <f t="shared" si="7"/>
-        <v>131.42906486238394</v>
+        <f t="shared" si="9"/>
+        <v>33.629596583034584</v>
       </c>
     </row>
     <row r="12" spans="2:140" x14ac:dyDescent="0.3">
@@ -1447,61 +1557,74 @@
       <c r="D12" s="3">
         <v>0</v>
       </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="11">
+        <f t="shared" ref="F12:F13" si="10">M12-E12-D12-C12</f>
+        <v>0</v>
+      </c>
       <c r="G12" s="3">
         <v>0</v>
       </c>
       <c r="H12" s="3">
         <v>0</v>
       </c>
+      <c r="I12" s="3">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3">
+        <v>0</v>
+      </c>
       <c r="L12" s="3">
         <v>0</v>
       </c>
       <c r="M12" s="3">
         <v>0</v>
       </c>
-      <c r="N12" s="3">
-        <f>N11*0.2</f>
-        <v>-5.9461999999999975</v>
+      <c r="N12" s="11">
+        <f t="shared" ref="N12:N13" si="11">SUM(G12:J12)</f>
+        <v>0</v>
       </c>
       <c r="O12" s="3">
-        <f t="shared" ref="O12:X12" si="8">O11*0.2</f>
-        <v>-3.3993499999999983</v>
+        <f t="shared" ref="O12:X12" si="12">O11*0.2</f>
+        <v>-5.6219999999999999</v>
       </c>
       <c r="P12" s="3">
-        <f t="shared" si="8"/>
-        <v>-2.1593599999999982</v>
+        <f t="shared" si="12"/>
+        <v>-5.6601999999999997</v>
       </c>
       <c r="Q12" s="3">
-        <f t="shared" si="8"/>
-        <v>0.40398000000000711</v>
+        <f t="shared" si="12"/>
+        <v>-4.7316299999999982</v>
       </c>
       <c r="R12" s="3">
-        <f t="shared" si="8"/>
-        <v>4.5775290000000153</v>
+        <f t="shared" si="12"/>
+        <v>-3.0762174999999958</v>
       </c>
       <c r="S12" s="3">
-        <f t="shared" si="8"/>
-        <v>10.232004450000018</v>
+        <f t="shared" si="12"/>
+        <v>-0.39440787499999036</v>
       </c>
       <c r="T12" s="3">
-        <f t="shared" si="8"/>
-        <v>16.501991602500016</v>
+        <f t="shared" si="12"/>
+        <v>2.8228061562500102</v>
       </c>
       <c r="U12" s="3">
-        <f t="shared" si="8"/>
-        <v>22.640899779000019</v>
+        <f t="shared" si="12"/>
+        <v>6.3991907475000067</v>
       </c>
       <c r="V12" s="3">
-        <f t="shared" si="8"/>
-        <v>25.213728771450032</v>
+        <f t="shared" si="12"/>
+        <v>7.4570872796250232</v>
       </c>
       <c r="W12" s="3">
-        <f t="shared" si="8"/>
-        <v>25.034107592835042</v>
+        <f t="shared" si="12"/>
+        <v>6.4056374443875264</v>
       </c>
       <c r="X12" s="3">
-        <f t="shared" si="8"/>
-        <v>26.285812972476791</v>
+        <f t="shared" si="12"/>
+        <v>6.7259193166069169</v>
       </c>
     </row>
     <row r="13" spans="2:140" x14ac:dyDescent="0.3">
@@ -1514,10 +1637,23 @@
       <c r="D13" s="3">
         <v>2</v>
       </c>
+      <c r="E13" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="F13" s="11">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
       <c r="G13" s="3">
         <v>0</v>
       </c>
       <c r="H13" s="3">
+        <v>0</v>
+      </c>
+      <c r="I13" s="3">
+        <v>0</v>
+      </c>
+      <c r="J13" s="3">
         <v>0</v>
       </c>
       <c r="L13" s="3">
@@ -1526,49 +1662,49 @@
       <c r="M13" s="3">
         <v>2.7</v>
       </c>
-      <c r="N13" s="3">
-        <f>N11*0.1</f>
-        <v>-2.9730999999999987</v>
+      <c r="N13" s="11">
+        <f t="shared" si="11"/>
+        <v>0</v>
       </c>
       <c r="O13" s="3">
-        <f t="shared" ref="O13:X13" si="9">O11*0.1</f>
-        <v>-1.6996749999999992</v>
+        <f t="shared" ref="O13:X13" si="13">O11*0.1</f>
+        <v>-2.8109999999999999</v>
       </c>
       <c r="P13" s="3">
-        <f t="shared" si="9"/>
-        <v>-1.0796799999999991</v>
+        <f t="shared" si="13"/>
+        <v>-2.8300999999999998</v>
       </c>
       <c r="Q13" s="3">
-        <f t="shared" si="9"/>
-        <v>0.20199000000000356</v>
+        <f t="shared" si="13"/>
+        <v>-2.3658149999999991</v>
       </c>
       <c r="R13" s="3">
-        <f t="shared" si="9"/>
-        <v>2.2887645000000076</v>
+        <f t="shared" si="13"/>
+        <v>-1.5381087499999979</v>
       </c>
       <c r="S13" s="3">
-        <f t="shared" si="9"/>
-        <v>5.1160022250000088</v>
+        <f t="shared" si="13"/>
+        <v>-0.19720393749999518</v>
       </c>
       <c r="T13" s="3">
-        <f t="shared" si="9"/>
-        <v>8.2509958012500082</v>
+        <f t="shared" si="13"/>
+        <v>1.4114030781250051</v>
       </c>
       <c r="U13" s="3">
-        <f t="shared" si="9"/>
-        <v>11.32044988950001</v>
+        <f t="shared" si="13"/>
+        <v>3.1995953737500034</v>
       </c>
       <c r="V13" s="3">
-        <f t="shared" si="9"/>
-        <v>12.606864385725016</v>
+        <f t="shared" si="13"/>
+        <v>3.7285436398125116</v>
       </c>
       <c r="W13" s="3">
-        <f t="shared" si="9"/>
-        <v>12.517053796417521</v>
+        <f t="shared" si="13"/>
+        <v>3.2028187221937632</v>
       </c>
       <c r="X13" s="3">
-        <f t="shared" si="9"/>
-        <v>13.142906486238395</v>
+        <f t="shared" si="13"/>
+        <v>3.3629596583034584</v>
       </c>
     </row>
     <row r="14" spans="2:140" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1583,6 +1719,14 @@
         <f>D11-D12-D13</f>
         <v>-12.599999999999998</v>
       </c>
+      <c r="E14" s="8">
+        <f>E11-E12-E13</f>
+        <v>-9.6999999999999993</v>
+      </c>
+      <c r="F14" s="8">
+        <f>F11-F12-F13</f>
+        <v>-10.199999999999998</v>
+      </c>
       <c r="G14" s="8">
         <f>G11-G12-G13</f>
         <v>-8.2000000000000028</v>
@@ -1591,6 +1735,14 @@
         <f>H11-H12-H13</f>
         <v>-8.5</v>
       </c>
+      <c r="I14" s="8">
+        <f>I11-I12-I13</f>
+        <v>-9.0000000000000036</v>
+      </c>
+      <c r="J14" s="8">
+        <f>J11-J12-J13</f>
+        <v>-9.4300000000000015</v>
+      </c>
       <c r="L14" s="8">
         <f>L11-L12-L13</f>
         <v>-52.2</v>
@@ -1601,511 +1753,511 @@
       </c>
       <c r="N14" s="8">
         <f>N11-N12-N13</f>
-        <v>-20.811699999999991</v>
+        <v>-35.13000000000001</v>
       </c>
       <c r="O14" s="8">
-        <f t="shared" ref="O14:X14" si="10">O11-O12-O13</f>
-        <v>-11.897724999999994</v>
+        <f t="shared" ref="O14:X14" si="14">O11-O12-O13</f>
+        <v>-19.677</v>
       </c>
       <c r="P14" s="8">
-        <f t="shared" si="10"/>
-        <v>-7.5577599999999938</v>
+        <f t="shared" si="14"/>
+        <v>-19.810699999999997</v>
       </c>
       <c r="Q14" s="8">
-        <f t="shared" si="10"/>
-        <v>1.4139300000000246</v>
+        <f t="shared" si="14"/>
+        <v>-16.560704999999995</v>
       </c>
       <c r="R14" s="8">
-        <f t="shared" si="10"/>
-        <v>16.021351500000055</v>
+        <f t="shared" si="14"/>
+        <v>-10.766761249999986</v>
       </c>
       <c r="S14" s="8">
-        <f t="shared" si="10"/>
-        <v>35.812015575000054</v>
+        <f t="shared" si="14"/>
+        <v>-1.380427562499966</v>
       </c>
       <c r="T14" s="8">
-        <f t="shared" si="10"/>
-        <v>57.756970608750059</v>
+        <f t="shared" si="14"/>
+        <v>9.8798215468750357</v>
       </c>
       <c r="U14" s="8">
-        <f t="shared" si="10"/>
-        <v>79.243149226500051</v>
+        <f t="shared" si="14"/>
+        <v>22.39716761625002</v>
       </c>
       <c r="V14" s="8">
-        <f t="shared" si="10"/>
-        <v>88.248050700075098</v>
+        <f t="shared" si="14"/>
+        <v>26.099805478687582</v>
       </c>
       <c r="W14" s="8">
-        <f t="shared" si="10"/>
-        <v>87.619376574922626</v>
+        <f t="shared" si="14"/>
+        <v>22.419731055356337</v>
       </c>
       <c r="X14" s="8">
-        <f t="shared" si="10"/>
-        <v>92.000345403668746</v>
+        <f t="shared" si="14"/>
+        <v>23.540717608124208</v>
       </c>
       <c r="Y14" s="1">
         <f>X14*(1+$AA$19)</f>
-        <v>91.080341949632057</v>
+        <v>23.305310432042965</v>
       </c>
       <c r="Z14" s="1">
-        <f t="shared" ref="Z14:CK14" si="11">Y14*(1+$AA$19)</f>
-        <v>90.169538530135739</v>
+        <f t="shared" ref="Z14:CK14" si="15">Y14*(1+$AA$19)</f>
+        <v>23.072257327722536</v>
       </c>
       <c r="AA14" s="1">
-        <f t="shared" si="11"/>
-        <v>89.267843144834387</v>
+        <f t="shared" si="15"/>
+        <v>22.841534754445309</v>
       </c>
       <c r="AB14" s="1">
-        <f t="shared" si="11"/>
-        <v>88.375164713386042</v>
+        <f t="shared" si="15"/>
+        <v>22.613119406900857</v>
       </c>
       <c r="AC14" s="1">
-        <f t="shared" si="11"/>
-        <v>87.491413066252179</v>
+        <f t="shared" si="15"/>
+        <v>22.386988212831849</v>
       </c>
       <c r="AD14" s="1">
-        <f t="shared" si="11"/>
-        <v>86.616498935589661</v>
+        <f t="shared" si="15"/>
+        <v>22.163118330703529</v>
       </c>
       <c r="AE14" s="1">
-        <f t="shared" si="11"/>
-        <v>85.750333946233766</v>
+        <f t="shared" si="15"/>
+        <v>21.941487147396494</v>
       </c>
       <c r="AF14" s="1">
-        <f t="shared" si="11"/>
-        <v>84.892830606771426</v>
+        <f t="shared" si="15"/>
+        <v>21.722072275922528</v>
       </c>
       <c r="AG14" s="1">
-        <f t="shared" si="11"/>
-        <v>84.043902300703706</v>
+        <f t="shared" si="15"/>
+        <v>21.504851553163302</v>
       </c>
       <c r="AH14" s="1">
-        <f t="shared" si="11"/>
-        <v>83.20346327769667</v>
+        <f t="shared" si="15"/>
+        <v>21.289803037631668</v>
       </c>
       <c r="AI14" s="1">
-        <f t="shared" si="11"/>
-        <v>82.371428644919703</v>
+        <f t="shared" si="15"/>
+        <v>21.076905007255352</v>
       </c>
       <c r="AJ14" s="1">
-        <f t="shared" si="11"/>
-        <v>81.5477143584705</v>
+        <f t="shared" si="15"/>
+        <v>20.866135957182799</v>
       </c>
       <c r="AK14" s="1">
-        <f t="shared" si="11"/>
-        <v>80.732237214885799</v>
+        <f t="shared" si="15"/>
+        <v>20.657474597610971</v>
       </c>
       <c r="AL14" s="1">
-        <f t="shared" si="11"/>
-        <v>79.924914842736939</v>
+        <f t="shared" si="15"/>
+        <v>20.450899851634862</v>
       </c>
       <c r="AM14" s="1">
-        <f t="shared" si="11"/>
-        <v>79.125665694309575</v>
+        <f t="shared" si="15"/>
+        <v>20.246390853118513</v>
       </c>
       <c r="AN14" s="1">
-        <f t="shared" si="11"/>
-        <v>78.334409037366484</v>
+        <f t="shared" si="15"/>
+        <v>20.043926944587326</v>
       </c>
       <c r="AO14" s="1">
-        <f t="shared" si="11"/>
-        <v>77.551064946992824</v>
+        <f t="shared" si="15"/>
+        <v>19.843487675141454</v>
       </c>
       <c r="AP14" s="1">
-        <f t="shared" si="11"/>
-        <v>76.775554297522902</v>
+        <f t="shared" si="15"/>
+        <v>19.64505279839004</v>
       </c>
       <c r="AQ14" s="1">
-        <f t="shared" si="11"/>
-        <v>76.007798754547679</v>
+        <f t="shared" si="15"/>
+        <v>19.448602270406141</v>
       </c>
       <c r="AR14" s="1">
-        <f t="shared" si="11"/>
-        <v>75.247720767002207</v>
+        <f t="shared" si="15"/>
+        <v>19.254116247702079</v>
       </c>
       <c r="AS14" s="1">
-        <f t="shared" si="11"/>
-        <v>74.495243559332181</v>
+        <f t="shared" si="15"/>
+        <v>19.061575085225059</v>
       </c>
       <c r="AT14" s="1">
-        <f t="shared" si="11"/>
-        <v>73.750291123738862</v>
+        <f t="shared" si="15"/>
+        <v>18.870959334372809</v>
       </c>
       <c r="AU14" s="1">
-        <f t="shared" si="11"/>
-        <v>73.012788212501476</v>
+        <f t="shared" si="15"/>
+        <v>18.682249741029082</v>
       </c>
       <c r="AV14" s="1">
-        <f t="shared" si="11"/>
-        <v>72.282660330376459</v>
+        <f t="shared" si="15"/>
+        <v>18.495427243618792</v>
       </c>
       <c r="AW14" s="1">
-        <f t="shared" si="11"/>
-        <v>71.5598337270727</v>
+        <f t="shared" si="15"/>
+        <v>18.310472971182605</v>
       </c>
       <c r="AX14" s="1">
-        <f t="shared" si="11"/>
-        <v>70.844235389801966</v>
+        <f t="shared" si="15"/>
+        <v>18.12736824147078</v>
       </c>
       <c r="AY14" s="1">
-        <f t="shared" si="11"/>
-        <v>70.135793035903944</v>
+        <f t="shared" si="15"/>
+        <v>17.946094559056071</v>
       </c>
       <c r="AZ14" s="1">
-        <f t="shared" si="11"/>
-        <v>69.434435105544907</v>
+        <f t="shared" si="15"/>
+        <v>17.766633613465512</v>
       </c>
       <c r="BA14" s="1">
-        <f t="shared" si="11"/>
-        <v>68.740090754489458</v>
+        <f t="shared" si="15"/>
+        <v>17.588967277330855</v>
       </c>
       <c r="BB14" s="1">
-        <f t="shared" si="11"/>
-        <v>68.05268984694456</v>
+        <f t="shared" si="15"/>
+        <v>17.413077604557547</v>
       </c>
       <c r="BC14" s="1">
-        <f t="shared" si="11"/>
-        <v>67.372162948475108</v>
+        <f t="shared" si="15"/>
+        <v>17.23894682851197</v>
       </c>
       <c r="BD14" s="1">
-        <f t="shared" si="11"/>
-        <v>66.698441318990362</v>
+        <f t="shared" si="15"/>
+        <v>17.066557360226852</v>
       </c>
       <c r="BE14" s="1">
-        <f t="shared" si="11"/>
-        <v>66.031456905800454</v>
+        <f t="shared" si="15"/>
+        <v>16.895891786624585</v>
       </c>
       <c r="BF14" s="1">
-        <f t="shared" si="11"/>
-        <v>65.371142336742452</v>
+        <f t="shared" si="15"/>
+        <v>16.72693286875834</v>
       </c>
       <c r="BG14" s="1">
-        <f t="shared" si="11"/>
-        <v>64.717430913375026</v>
+        <f t="shared" si="15"/>
+        <v>16.559663540070755</v>
       </c>
       <c r="BH14" s="1">
-        <f t="shared" si="11"/>
-        <v>64.07025660424128</v>
+        <f t="shared" si="15"/>
+        <v>16.394066904670048</v>
       </c>
       <c r="BI14" s="1">
-        <f t="shared" si="11"/>
-        <v>63.429554038198866</v>
+        <f t="shared" si="15"/>
+        <v>16.230126235623349</v>
       </c>
       <c r="BJ14" s="1">
-        <f t="shared" si="11"/>
-        <v>62.795258497816874</v>
+        <f t="shared" si="15"/>
+        <v>16.067824973267115</v>
       </c>
       <c r="BK14" s="1">
-        <f t="shared" si="11"/>
-        <v>62.167305912838707</v>
+        <f t="shared" si="15"/>
+        <v>15.907146723534444</v>
       </c>
       <c r="BL14" s="1">
-        <f t="shared" si="11"/>
-        <v>61.545632853710316</v>
+        <f t="shared" si="15"/>
+        <v>15.748075256299099</v>
       </c>
       <c r="BM14" s="1">
-        <f t="shared" si="11"/>
-        <v>60.930176525173209</v>
+        <f t="shared" si="15"/>
+        <v>15.590594503736108</v>
       </c>
       <c r="BN14" s="1">
-        <f t="shared" si="11"/>
-        <v>60.320874759921473</v>
+        <f t="shared" si="15"/>
+        <v>15.434688558698747</v>
       </c>
       <c r="BO14" s="1">
-        <f t="shared" si="11"/>
-        <v>59.717666012322255</v>
+        <f t="shared" si="15"/>
+        <v>15.28034167311176</v>
       </c>
       <c r="BP14" s="1">
-        <f t="shared" si="11"/>
-        <v>59.12048935219903</v>
+        <f t="shared" si="15"/>
+        <v>15.127538256380642</v>
       </c>
       <c r="BQ14" s="1">
-        <f t="shared" si="11"/>
-        <v>58.52928445867704</v>
+        <f t="shared" si="15"/>
+        <v>14.976262873816836</v>
       </c>
       <c r="BR14" s="1">
-        <f t="shared" si="11"/>
-        <v>57.943991614090272</v>
+        <f t="shared" si="15"/>
+        <v>14.826500245078668</v>
       </c>
       <c r="BS14" s="1">
-        <f t="shared" si="11"/>
-        <v>57.364551697949366</v>
+        <f t="shared" si="15"/>
+        <v>14.678235242627881</v>
       </c>
       <c r="BT14" s="1">
-        <f t="shared" si="11"/>
-        <v>56.79090618096987</v>
+        <f t="shared" si="15"/>
+        <v>14.531452890201603</v>
       </c>
       <c r="BU14" s="1">
-        <f t="shared" si="11"/>
-        <v>56.222997119160169</v>
+        <f t="shared" si="15"/>
+        <v>14.386138361299587</v>
       </c>
       <c r="BV14" s="1">
-        <f t="shared" si="11"/>
-        <v>55.660767147968564</v>
+        <f t="shared" si="15"/>
+        <v>14.24227697768659</v>
       </c>
       <c r="BW14" s="1">
-        <f t="shared" si="11"/>
-        <v>55.104159476488874</v>
+        <f t="shared" si="15"/>
+        <v>14.099854207909724</v>
       </c>
       <c r="BX14" s="1">
-        <f t="shared" si="11"/>
-        <v>54.553117881723985</v>
+        <f t="shared" si="15"/>
+        <v>13.958855665830626</v>
       </c>
       <c r="BY14" s="1">
-        <f t="shared" si="11"/>
-        <v>54.007586702906742</v>
+        <f t="shared" si="15"/>
+        <v>13.819267109172319</v>
       </c>
       <c r="BZ14" s="1">
-        <f t="shared" si="11"/>
-        <v>53.467510835877675</v>
+        <f t="shared" si="15"/>
+        <v>13.681074438080596</v>
       </c>
       <c r="CA14" s="1">
-        <f t="shared" si="11"/>
-        <v>52.932835727518899</v>
+        <f t="shared" si="15"/>
+        <v>13.54426369369979</v>
       </c>
       <c r="CB14" s="1">
-        <f t="shared" si="11"/>
-        <v>52.403507370243709</v>
+        <f t="shared" si="15"/>
+        <v>13.408821056762791</v>
       </c>
       <c r="CC14" s="1">
-        <f t="shared" si="11"/>
-        <v>51.879472296541273</v>
+        <f t="shared" si="15"/>
+        <v>13.274732846195164</v>
       </c>
       <c r="CD14" s="1">
-        <f t="shared" si="11"/>
-        <v>51.360677573575863</v>
+        <f t="shared" si="15"/>
+        <v>13.141985517733213</v>
       </c>
       <c r="CE14" s="1">
-        <f t="shared" si="11"/>
-        <v>50.847070797840104</v>
+        <f t="shared" si="15"/>
+        <v>13.01056566255588</v>
       </c>
       <c r="CF14" s="1">
-        <f t="shared" si="11"/>
-        <v>50.3386000898617</v>
+        <f t="shared" si="15"/>
+        <v>12.88046000593032</v>
       </c>
       <c r="CG14" s="1">
-        <f t="shared" si="11"/>
-        <v>49.835214088963085</v>
+        <f t="shared" si="15"/>
+        <v>12.751655405871016</v>
       </c>
       <c r="CH14" s="1">
-        <f t="shared" si="11"/>
-        <v>49.336861948073455</v>
+        <f t="shared" si="15"/>
+        <v>12.624138851812306</v>
       </c>
       <c r="CI14" s="1">
-        <f t="shared" si="11"/>
-        <v>48.843493328592722</v>
+        <f t="shared" si="15"/>
+        <v>12.497897463294183</v>
       </c>
       <c r="CJ14" s="1">
-        <f t="shared" si="11"/>
-        <v>48.355058395306791</v>
+        <f t="shared" si="15"/>
+        <v>12.372918488661242</v>
       </c>
       <c r="CK14" s="1">
-        <f t="shared" si="11"/>
-        <v>47.871507811353723</v>
+        <f t="shared" si="15"/>
+        <v>12.24918930377463</v>
       </c>
       <c r="CL14" s="1">
-        <f t="shared" ref="CL14:EJ14" si="12">CK14*(1+$AA$19)</f>
-        <v>47.392792733240185</v>
+        <f t="shared" ref="CL14:EJ14" si="16">CK14*(1+$AA$19)</f>
+        <v>12.126697410736883</v>
       </c>
       <c r="CM14" s="1">
-        <f t="shared" si="12"/>
-        <v>46.918864805907781</v>
+        <f t="shared" si="16"/>
+        <v>12.005430436629513</v>
       </c>
       <c r="CN14" s="1">
-        <f t="shared" si="12"/>
-        <v>46.4496761578487</v>
+        <f t="shared" si="16"/>
+        <v>11.885376132263218</v>
       </c>
       <c r="CO14" s="1">
-        <f t="shared" si="12"/>
-        <v>45.985179396270212</v>
+        <f t="shared" si="16"/>
+        <v>11.766522370940585</v>
       </c>
       <c r="CP14" s="1">
-        <f t="shared" si="12"/>
-        <v>45.525327602307506</v>
+        <f t="shared" si="16"/>
+        <v>11.64885714723118</v>
       </c>
       <c r="CQ14" s="1">
-        <f t="shared" si="12"/>
-        <v>45.070074326284427</v>
+        <f t="shared" si="16"/>
+        <v>11.532368575758868</v>
       </c>
       <c r="CR14" s="1">
-        <f t="shared" si="12"/>
-        <v>44.619373583021584</v>
+        <f t="shared" si="16"/>
+        <v>11.417044890001279</v>
       </c>
       <c r="CS14" s="1">
-        <f t="shared" si="12"/>
-        <v>44.173179847191371</v>
+        <f t="shared" si="16"/>
+        <v>11.302874441101265</v>
       </c>
       <c r="CT14" s="1">
-        <f t="shared" si="12"/>
-        <v>43.731448048719457</v>
+        <f t="shared" si="16"/>
+        <v>11.189845696690252</v>
       </c>
       <c r="CU14" s="1">
-        <f t="shared" si="12"/>
-        <v>43.294133568232262</v>
+        <f t="shared" si="16"/>
+        <v>11.077947239723349</v>
       </c>
       <c r="CV14" s="1">
-        <f t="shared" si="12"/>
-        <v>42.861192232549939</v>
+        <f t="shared" si="16"/>
+        <v>10.967167767326115</v>
       </c>
       <c r="CW14" s="1">
-        <f t="shared" si="12"/>
-        <v>42.432580310224438</v>
+        <f t="shared" si="16"/>
+        <v>10.857496089652853</v>
       </c>
       <c r="CX14" s="1">
-        <f t="shared" si="12"/>
-        <v>42.008254507122196</v>
+        <f t="shared" si="16"/>
+        <v>10.748921128756324</v>
       </c>
       <c r="CY14" s="1">
-        <f t="shared" si="12"/>
-        <v>41.588171962050971</v>
+        <f t="shared" si="16"/>
+        <v>10.641431917468761</v>
       </c>
       <c r="CZ14" s="1">
-        <f t="shared" si="12"/>
-        <v>41.172290242430464</v>
+        <f t="shared" si="16"/>
+        <v>10.535017598294074</v>
       </c>
       <c r="DA14" s="1">
-        <f t="shared" si="12"/>
-        <v>40.760567340006162</v>
+        <f t="shared" si="16"/>
+        <v>10.429667422311132</v>
       </c>
       <c r="DB14" s="1">
-        <f t="shared" si="12"/>
-        <v>40.352961666606099</v>
+        <f t="shared" si="16"/>
+        <v>10.325370748088021</v>
       </c>
       <c r="DC14" s="1">
-        <f t="shared" si="12"/>
-        <v>39.949432049940036</v>
+        <f t="shared" si="16"/>
+        <v>10.222117040607142</v>
       </c>
       <c r="DD14" s="1">
-        <f t="shared" si="12"/>
-        <v>39.549937729440636</v>
+        <f t="shared" si="16"/>
+        <v>10.11989587020107</v>
       </c>
       <c r="DE14" s="1">
-        <f t="shared" si="12"/>
-        <v>39.154438352146229</v>
+        <f t="shared" si="16"/>
+        <v>10.01869691149906</v>
       </c>
       <c r="DF14" s="1">
-        <f t="shared" si="12"/>
-        <v>38.762893968624766</v>
+        <f t="shared" si="16"/>
+        <v>9.9185099423840697</v>
       </c>
       <c r="DG14" s="1">
-        <f t="shared" si="12"/>
-        <v>38.375265028938522</v>
+        <f t="shared" si="16"/>
+        <v>9.8193248429602296</v>
       </c>
       <c r="DH14" s="1">
-        <f t="shared" si="12"/>
-        <v>37.991512378649134</v>
+        <f t="shared" si="16"/>
+        <v>9.7211315945306271</v>
       </c>
       <c r="DI14" s="1">
-        <f t="shared" si="12"/>
-        <v>37.611597254862644</v>
+        <f t="shared" si="16"/>
+        <v>9.6239202785853202</v>
       </c>
       <c r="DJ14" s="1">
-        <f t="shared" si="12"/>
-        <v>37.235481282314019</v>
+        <f t="shared" si="16"/>
+        <v>9.5276810757994674</v>
       </c>
       <c r="DK14" s="1">
-        <f t="shared" si="12"/>
-        <v>36.863126469490879</v>
+        <f t="shared" si="16"/>
+        <v>9.4324042650414732</v>
       </c>
       <c r="DL14" s="1">
-        <f t="shared" si="12"/>
-        <v>36.494495204795967</v>
+        <f t="shared" si="16"/>
+        <v>9.3380802223910582</v>
       </c>
       <c r="DM14" s="1">
-        <f t="shared" si="12"/>
-        <v>36.129550252748004</v>
+        <f t="shared" si="16"/>
+        <v>9.244699420167148</v>
       </c>
       <c r="DN14" s="1">
-        <f t="shared" si="12"/>
-        <v>35.768254750220521</v>
+        <f t="shared" si="16"/>
+        <v>9.1522524259654769</v>
       </c>
       <c r="DO14" s="1">
-        <f t="shared" si="12"/>
-        <v>35.410572202718313</v>
+        <f t="shared" si="16"/>
+        <v>9.0607299017058214</v>
       </c>
       <c r="DP14" s="1">
-        <f t="shared" si="12"/>
-        <v>35.056466480691128</v>
+        <f t="shared" si="16"/>
+        <v>8.9701226026887628</v>
       </c>
       <c r="DQ14" s="1">
-        <f t="shared" si="12"/>
-        <v>34.705901815884218</v>
+        <f t="shared" si="16"/>
+        <v>8.8804213766618751</v>
       </c>
       <c r="DR14" s="1">
-        <f t="shared" si="12"/>
-        <v>34.358842797725373</v>
+        <f t="shared" si="16"/>
+        <v>8.7916171628952569</v>
       </c>
       <c r="DS14" s="1">
-        <f t="shared" si="12"/>
-        <v>34.015254369748121</v>
+        <f t="shared" si="16"/>
+        <v>8.7037009912663041</v>
       </c>
       <c r="DT14" s="1">
-        <f t="shared" si="12"/>
-        <v>33.675101826050636</v>
+        <f t="shared" si="16"/>
+        <v>8.616663981353641</v>
       </c>
       <c r="DU14" s="1">
-        <f t="shared" si="12"/>
-        <v>33.338350807790128</v>
+        <f t="shared" si="16"/>
+        <v>8.5304973415401051</v>
       </c>
       <c r="DV14" s="1">
-        <f t="shared" si="12"/>
-        <v>33.004967299712227</v>
+        <f t="shared" si="16"/>
+        <v>8.4451923681247045</v>
       </c>
       <c r="DW14" s="1">
-        <f t="shared" si="12"/>
-        <v>32.674917626715107</v>
+        <f t="shared" si="16"/>
+        <v>8.3607404444434579</v>
       </c>
       <c r="DX14" s="1">
-        <f t="shared" si="12"/>
-        <v>32.348168450447957</v>
+        <f t="shared" si="16"/>
+        <v>8.2771330399990237</v>
       </c>
       <c r="DY14" s="1">
-        <f t="shared" si="12"/>
-        <v>32.024686765943478</v>
+        <f t="shared" si="16"/>
+        <v>8.1943617095990327</v>
       </c>
       <c r="DZ14" s="1">
-        <f t="shared" si="12"/>
-        <v>31.704439898284043</v>
+        <f t="shared" si="16"/>
+        <v>8.1124180925030416</v>
       </c>
       <c r="EA14" s="1">
-        <f t="shared" si="12"/>
-        <v>31.387395499301203</v>
+        <f t="shared" si="16"/>
+        <v>8.0312939115780111</v>
       </c>
       <c r="EB14" s="1">
-        <f t="shared" si="12"/>
-        <v>31.073521544308189</v>
+        <f t="shared" si="16"/>
+        <v>7.9509809724622311</v>
       </c>
       <c r="EC14" s="1">
-        <f t="shared" si="12"/>
-        <v>30.762786328865108</v>
+        <f t="shared" si="16"/>
+        <v>7.8714711627376088</v>
       </c>
       <c r="ED14" s="1">
-        <f t="shared" si="12"/>
-        <v>30.455158465576456</v>
+        <f t="shared" si="16"/>
+        <v>7.7927564511102325</v>
       </c>
       <c r="EE14" s="1">
-        <f t="shared" si="12"/>
-        <v>30.150606880920691</v>
+        <f t="shared" si="16"/>
+        <v>7.7148288865991299</v>
       </c>
       <c r="EF14" s="1">
-        <f t="shared" si="12"/>
-        <v>29.849100812111484</v>
+        <f t="shared" si="16"/>
+        <v>7.6376805977331381</v>
       </c>
       <c r="EG14" s="1">
-        <f t="shared" si="12"/>
-        <v>29.550609803990369</v>
+        <f t="shared" si="16"/>
+        <v>7.5613037917558064</v>
       </c>
       <c r="EH14" s="1">
-        <f t="shared" si="12"/>
-        <v>29.255103705950464</v>
+        <f t="shared" si="16"/>
+        <v>7.4856907538382487</v>
       </c>
       <c r="EI14" s="1">
-        <f t="shared" si="12"/>
-        <v>28.962552668890961</v>
+        <f t="shared" si="16"/>
+        <v>7.410833846299866</v>
       </c>
       <c r="EJ14" s="1">
-        <f t="shared" si="12"/>
-        <v>28.672927142202052</v>
+        <f t="shared" si="16"/>
+        <v>7.3367255078368672</v>
       </c>
     </row>
     <row r="15" spans="2:140" x14ac:dyDescent="0.3">
@@ -2120,6 +2272,14 @@
         <f>17.5</f>
         <v>17.5</v>
       </c>
+      <c r="E15" s="3">
+        <f>18.3</f>
+        <v>18.3</v>
+      </c>
+      <c r="F15" s="3">
+        <f>18.3</f>
+        <v>18.3</v>
+      </c>
       <c r="G15" s="3">
         <f>17.5</f>
         <v>17.5</v>
@@ -2128,6 +2288,14 @@
         <f>18.2</f>
         <v>18.2</v>
       </c>
+      <c r="I15" s="3">
+        <f>18.3</f>
+        <v>18.3</v>
+      </c>
+      <c r="J15" s="3">
+        <f>18.3</f>
+        <v>18.3</v>
+      </c>
       <c r="L15" s="3">
         <f>17.5</f>
         <v>17.5</v>
@@ -2137,48 +2305,48 @@
         <v>17.5</v>
       </c>
       <c r="N15" s="3">
-        <f>18.2</f>
-        <v>18.2</v>
+        <f>18.3</f>
+        <v>18.3</v>
       </c>
       <c r="O15" s="3">
-        <f>18.2</f>
-        <v>18.2</v>
+        <f>18.3</f>
+        <v>18.3</v>
       </c>
       <c r="P15" s="3">
-        <f>18.2</f>
-        <v>18.2</v>
+        <f>18.3</f>
+        <v>18.3</v>
       </c>
       <c r="Q15" s="3">
-        <f>18.2</f>
-        <v>18.2</v>
+        <f>18.3</f>
+        <v>18.3</v>
       </c>
       <c r="R15" s="3">
-        <f>18.2</f>
-        <v>18.2</v>
+        <f>18.3</f>
+        <v>18.3</v>
       </c>
       <c r="S15" s="3">
-        <f>18.2</f>
-        <v>18.2</v>
+        <f>18.3</f>
+        <v>18.3</v>
       </c>
       <c r="T15" s="3">
-        <f>18.2</f>
-        <v>18.2</v>
+        <f>18.3</f>
+        <v>18.3</v>
       </c>
       <c r="U15" s="3">
-        <f>18.2</f>
-        <v>18.2</v>
+        <f>18.3</f>
+        <v>18.3</v>
       </c>
       <c r="V15" s="3">
-        <f>18.2</f>
-        <v>18.2</v>
+        <f>18.3</f>
+        <v>18.3</v>
       </c>
       <c r="W15" s="3">
-        <f>18.2</f>
-        <v>18.2</v>
+        <f>18.3</f>
+        <v>18.3</v>
       </c>
       <c r="X15" s="3">
-        <f>18.2</f>
-        <v>18.2</v>
+        <f>18.3</f>
+        <v>18.3</v>
       </c>
     </row>
     <row r="16" spans="2:140" x14ac:dyDescent="0.3">
@@ -2193,6 +2361,14 @@
         <f>D14/D15</f>
         <v>-0.71999999999999986</v>
       </c>
+      <c r="E16" s="7">
+        <f>E14/E15</f>
+        <v>-0.53005464480874309</v>
+      </c>
+      <c r="F16" s="7">
+        <f>F14/F15</f>
+        <v>-0.55737704918032771</v>
+      </c>
       <c r="G16" s="7">
         <f>G14/G15</f>
         <v>-0.46857142857142875</v>
@@ -2201,6 +2377,14 @@
         <f>H14/H15</f>
         <v>-0.46703296703296704</v>
       </c>
+      <c r="I16" s="7">
+        <f>I14/I15</f>
+        <v>-0.49180327868852475</v>
+      </c>
+      <c r="J16" s="7">
+        <f>J14/J15</f>
+        <v>-0.51530054644808754</v>
+      </c>
       <c r="L16" s="7">
         <f>L14/L15</f>
         <v>-2.9828571428571431</v>
@@ -2211,47 +2395,47 @@
       </c>
       <c r="N16" s="7">
         <f>N14/N15</f>
-        <v>-1.1434999999999995</v>
+        <v>-1.9196721311475415</v>
       </c>
       <c r="O16" s="7">
-        <f t="shared" ref="O16:X16" si="13">O14/O15</f>
-        <v>-0.65372115384615359</v>
+        <f t="shared" ref="O16:X16" si="17">O14/O15</f>
+        <v>-1.0752459016393443</v>
       </c>
       <c r="P16" s="7">
-        <f t="shared" si="13"/>
-        <v>-0.41526153846153813</v>
+        <f t="shared" si="17"/>
+        <v>-1.0825519125683059</v>
       </c>
       <c r="Q16" s="7">
-        <f t="shared" si="13"/>
-        <v>7.7688461538462886E-2</v>
+        <f t="shared" si="17"/>
+        <v>-0.90495655737704883</v>
       </c>
       <c r="R16" s="7">
-        <f t="shared" si="13"/>
-        <v>0.88029403846154153</v>
+        <f t="shared" si="17"/>
+        <v>-0.58834760928961671</v>
       </c>
       <c r="S16" s="7">
-        <f t="shared" si="13"/>
-        <v>1.9676931634615416</v>
+        <f t="shared" si="17"/>
+        <v>-7.543320013661016E-2</v>
       </c>
       <c r="T16" s="7">
-        <f t="shared" si="13"/>
-        <v>3.1734599235576955</v>
+        <f t="shared" si="17"/>
+        <v>0.53988095884563037</v>
       </c>
       <c r="U16" s="7">
-        <f t="shared" si="13"/>
-        <v>4.3540191882692341</v>
+        <f t="shared" si="17"/>
+        <v>1.2238889407786895</v>
       </c>
       <c r="V16" s="7">
-        <f t="shared" si="13"/>
-        <v>4.848793994509621</v>
+        <f t="shared" si="17"/>
+        <v>1.4262188786168077</v>
       </c>
       <c r="W16" s="7">
-        <f t="shared" si="13"/>
-        <v>4.8142514601605839</v>
+        <f t="shared" si="17"/>
+        <v>1.2251219155932425</v>
       </c>
       <c r="X16" s="7">
-        <f t="shared" si="13"/>
-        <v>5.0549640331686128</v>
+        <f t="shared" si="17"/>
+        <v>1.2863780113729075</v>
       </c>
     </row>
     <row r="18" spans="2:27" x14ac:dyDescent="0.3">
@@ -2264,16 +2448,16 @@
         <v>3.289473684210531E-2</v>
       </c>
       <c r="H18" s="9">
-        <f t="shared" ref="H18:J18" si="14">H3/D3-1</f>
+        <f t="shared" ref="H18:J18" si="18">H3/D3-1</f>
         <v>-0.11822660098522175</v>
       </c>
       <c r="I18" s="9">
-        <f t="shared" si="14"/>
-        <v>-5.2631578947368474E-2</v>
+        <f t="shared" si="18"/>
+        <v>-0.10344827586206906</v>
       </c>
       <c r="J18" s="9">
-        <f t="shared" si="14"/>
-        <v>-0.24</v>
+        <f t="shared" si="18"/>
+        <v>-6.4039408866995107E-2</v>
       </c>
       <c r="L18" s="9"/>
       <c r="M18" s="9">
@@ -2281,47 +2465,47 @@
         <v>0.16183206106870229</v>
       </c>
       <c r="N18" s="9">
-        <f t="shared" ref="N18:X18" si="15">N3/M3-1</f>
-        <v>-7.2273324572930342E-2</v>
+        <f t="shared" ref="N18:X18" si="19">N3/M3-1</f>
+        <v>-6.9645203679369216E-2</v>
       </c>
       <c r="O18" s="9">
-        <f t="shared" si="15"/>
-        <v>0.16147308781869696</v>
+        <f t="shared" si="19"/>
+        <v>0.15819209039548032</v>
       </c>
       <c r="P18" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>0.70000000000000018</v>
       </c>
       <c r="Q18" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="R18" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>0.50000000000000022</v>
       </c>
       <c r="S18" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>0.39999999999999991</v>
       </c>
       <c r="T18" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="U18" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="V18" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="W18" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="X18" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>5.0000000000000044E-2</v>
       </c>
     </row>
@@ -2333,6 +2517,18 @@
         <f>C5/C3</f>
         <v>0.40789473684210525</v>
       </c>
+      <c r="D19" s="9">
+        <f>D5/D3</f>
+        <v>0.32019704433497537</v>
+      </c>
+      <c r="E19" s="9">
+        <f>E5/E3</f>
+        <v>0.32512315270935965</v>
+      </c>
+      <c r="F19" s="9">
+        <f>F5/F3</f>
+        <v>0.24630541871921216</v>
+      </c>
       <c r="G19" s="9">
         <f>G5/G3</f>
         <v>0.53503184713375784</v>
@@ -2341,6 +2537,14 @@
         <f>H5/H3</f>
         <v>0.4022346368715084</v>
       </c>
+      <c r="I19" s="9">
+        <f>I5/I3</f>
+        <v>0.42307692307692307</v>
+      </c>
+      <c r="J19" s="9">
+        <f>J5/J3</f>
+        <v>0.43</v>
+      </c>
       <c r="L19" s="9">
         <f>L5/L3</f>
         <v>0.29618320610687021</v>
@@ -2350,48 +2554,48 @@
         <v>0.31931668856767409</v>
       </c>
       <c r="N19" s="9">
-        <f t="shared" ref="N19:X19" si="16">N5/N3</f>
-        <v>0.54</v>
+        <f t="shared" ref="N19:X19" si="20">N5/N3</f>
+        <v>0.44449152542372883</v>
       </c>
       <c r="O19" s="9">
-        <f t="shared" si="16"/>
-        <v>0.54</v>
+        <f t="shared" si="20"/>
+        <v>0.42</v>
       </c>
       <c r="P19" s="9">
-        <f t="shared" si="16"/>
-        <v>0.54</v>
+        <f t="shared" si="20"/>
+        <v>0.43</v>
       </c>
       <c r="Q19" s="9">
-        <f t="shared" si="16"/>
-        <v>0.54</v>
+        <f t="shared" si="20"/>
+        <v>0.44</v>
       </c>
       <c r="R19" s="9">
-        <f t="shared" si="16"/>
-        <v>0.54</v>
+        <f t="shared" si="20"/>
+        <v>0.44</v>
       </c>
       <c r="S19" s="9">
-        <f t="shared" si="16"/>
-        <v>0.54</v>
+        <f t="shared" si="20"/>
+        <v>0.44</v>
       </c>
       <c r="T19" s="9">
-        <f t="shared" si="16"/>
-        <v>0.54</v>
+        <f t="shared" si="20"/>
+        <v>0.44</v>
       </c>
       <c r="U19" s="9">
-        <f t="shared" si="16"/>
-        <v>0.54</v>
+        <f t="shared" si="20"/>
+        <v>0.44</v>
       </c>
       <c r="V19" s="9">
-        <f t="shared" si="16"/>
-        <v>0.54</v>
+        <f t="shared" si="20"/>
+        <v>0.44</v>
       </c>
       <c r="W19" s="9">
-        <f t="shared" si="16"/>
-        <v>0.54</v>
+        <f t="shared" si="20"/>
+        <v>0.44</v>
       </c>
       <c r="X19" s="9">
-        <f t="shared" si="16"/>
-        <v>0.54</v>
+        <f t="shared" si="20"/>
+        <v>0.44000000000000006</v>
       </c>
       <c r="Z19" t="s">
         <v>39</v>
@@ -2405,6 +2609,9 @@
         <v>34</v>
       </c>
       <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
       <c r="G20" s="9">
         <f>G6/C6-1</f>
         <v>-7.4468085106383142E-2</v>
@@ -2412,6 +2619,14 @@
       <c r="H20" s="9">
         <f>H6/D6-1</f>
         <v>-5.3191489361702149E-2</v>
+      </c>
+      <c r="I20" s="9">
+        <f>I6/E6-1</f>
+        <v>-7.291666666666663E-2</v>
+      </c>
+      <c r="J20" s="9">
+        <f>J6/F6-1</f>
+        <v>3.4090909090908728E-2</v>
       </c>
       <c r="L20" s="9"/>
       <c r="M20" s="9">
@@ -2419,47 +2634,47 @@
         <v>-0.15454545454545443</v>
       </c>
       <c r="N20" s="9">
-        <f t="shared" ref="N20:X20" si="17">N6/M6-1</f>
-        <v>-3.2258064516129115E-2</v>
+        <f t="shared" ref="N20:X20" si="21">N6/M6-1</f>
+        <v>-4.3010752688172116E-2</v>
       </c>
       <c r="O20" s="9">
-        <f t="shared" si="17"/>
-        <v>-5.0000000000000155E-2</v>
+        <f t="shared" si="21"/>
+        <v>-5.0000000000000044E-2</v>
       </c>
       <c r="P20" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0.25</v>
       </c>
       <c r="Q20" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0.25</v>
       </c>
       <c r="R20" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0.25</v>
       </c>
       <c r="S20" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0.25</v>
       </c>
       <c r="T20" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0.25</v>
       </c>
       <c r="U20" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="V20" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0.14999999999999991</v>
       </c>
       <c r="W20" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="X20" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="Z20" t="s">
@@ -2474,6 +2689,9 @@
         <v>35</v>
       </c>
       <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
       <c r="G21" s="9">
         <f>G7/C7-1</f>
         <v>0.40000000000000013</v>
@@ -2481,6 +2699,14 @@
       <c r="H21" s="9">
         <f>H7/D7-1</f>
         <v>-0.11250000000000004</v>
+      </c>
+      <c r="I21" s="9">
+        <f>I7/E7-1</f>
+        <v>0.23943661971830998</v>
+      </c>
+      <c r="J21" s="9">
+        <f>J7/F7-1</f>
+        <v>0.439393939393939</v>
       </c>
       <c r="L21" s="9"/>
       <c r="M21" s="9">
@@ -2488,47 +2714,47 @@
         <v>3.7453183520599342E-2</v>
       </c>
       <c r="N21" s="9">
-        <f t="shared" ref="N21:X21" si="18">N7/M7-1</f>
-        <v>0.14999999999999991</v>
+        <f t="shared" ref="N21:X21" si="22">N7/M7-1</f>
+        <v>0.22021660649819497</v>
       </c>
       <c r="O21" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>-0.15000000000000002</v>
       </c>
       <c r="P21" s="9">
-        <f t="shared" si="18"/>
-        <v>0.60000000000000031</v>
+        <f t="shared" si="22"/>
+        <v>0.60000000000000009</v>
       </c>
       <c r="Q21" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>0.5</v>
       </c>
       <c r="R21" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>0.39999999999999991</v>
       </c>
       <c r="S21" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="T21" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="U21" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="V21" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="W21" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="X21" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="Z21" t="s">
@@ -2536,7 +2762,7 @@
       </c>
       <c r="AA21" s="3">
         <f>NPV(AA20,N14:EJ14)</f>
-        <v>393.22401453576623</v>
+        <v>21.524233178627995</v>
       </c>
     </row>
     <row r="22" spans="2:27" x14ac:dyDescent="0.3">
@@ -2547,6 +2773,18 @@
         <f>C7/C3</f>
         <v>0.39473684210526316</v>
       </c>
+      <c r="D22" s="9">
+        <f>D7/D3</f>
+        <v>0.39408866995073888</v>
+      </c>
+      <c r="E22" s="9">
+        <f>E7/E3</f>
+        <v>0.34975369458128075</v>
+      </c>
+      <c r="F22" s="9">
+        <f>F7/F3</f>
+        <v>0.32512315270935965</v>
+      </c>
       <c r="G22" s="9">
         <f>G7/G3</f>
         <v>0.53503184713375795</v>
@@ -2555,6 +2793,14 @@
         <f>H7/H3</f>
         <v>0.39664804469273746</v>
       </c>
+      <c r="I22" s="9">
+        <f>I7/I3</f>
+        <v>0.48351648351648358</v>
+      </c>
+      <c r="J22" s="9">
+        <f>J7/J3</f>
+        <v>0.5</v>
+      </c>
       <c r="L22" s="9">
         <f>L7/L3</f>
         <v>0.40763358778625952</v>
@@ -2564,55 +2810,55 @@
         <v>0.36399474375821289</v>
       </c>
       <c r="N22" s="9">
-        <f t="shared" ref="N22:X22" si="19">N7/N3</f>
-        <v>0.4512039660056657</v>
+        <f t="shared" ref="N22:X22" si="23">N7/N3</f>
+        <v>0.47740112994350281</v>
       </c>
       <c r="O22" s="9">
-        <f t="shared" si="19"/>
-        <v>0.3302042682926829</v>
+        <f t="shared" si="23"/>
+        <v>0.35036585365853656</v>
       </c>
       <c r="P22" s="9">
-        <f t="shared" si="19"/>
-        <v>0.31078048780487805</v>
+        <f t="shared" si="23"/>
+        <v>0.32975609756097557</v>
       </c>
       <c r="Q22" s="9">
-        <f t="shared" si="19"/>
-        <v>0.29135670731707314</v>
+        <f t="shared" si="23"/>
+        <v>0.30914634146341458</v>
       </c>
       <c r="R22" s="9">
-        <f t="shared" si="19"/>
-        <v>0.27193292682926823</v>
+        <f t="shared" si="23"/>
+        <v>0.28853658536585358</v>
       </c>
       <c r="S22" s="9">
-        <f t="shared" si="19"/>
-        <v>0.25250914634146338</v>
+        <f t="shared" si="23"/>
+        <v>0.26792682926829264</v>
       </c>
       <c r="T22" s="9">
-        <f t="shared" si="19"/>
-        <v>0.23308536585365852</v>
+        <f t="shared" si="23"/>
+        <v>0.24731707317073165</v>
       </c>
       <c r="U22" s="9">
-        <f t="shared" si="19"/>
-        <v>0.21366158536585364</v>
+        <f t="shared" si="23"/>
+        <v>0.22670731707317068</v>
       </c>
       <c r="V22" s="9">
-        <f t="shared" si="19"/>
-        <v>0.20394969512195119</v>
+        <f t="shared" si="23"/>
+        <v>0.21640243902439019</v>
       </c>
       <c r="W22" s="9">
-        <f t="shared" si="19"/>
-        <v>0.20394969512195119</v>
+        <f t="shared" si="23"/>
+        <v>0.21640243902439016</v>
       </c>
       <c r="X22" s="9">
-        <f t="shared" si="19"/>
-        <v>0.20394969512195121</v>
+        <f t="shared" si="23"/>
+        <v>0.21640243902439016</v>
       </c>
       <c r="Z22" t="s">
         <v>42</v>
       </c>
       <c r="AA22" s="3">
         <f>Main!D8</f>
-        <v>47.5</v>
+        <v>146.5</v>
       </c>
     </row>
     <row r="23" spans="2:27" x14ac:dyDescent="0.3">
@@ -2623,6 +2869,18 @@
         <f>C9/C3</f>
         <v>-0.60526315789473695</v>
       </c>
+      <c r="D23" s="9">
+        <f>D9/D3</f>
+        <v>-0.53694581280788167</v>
+      </c>
+      <c r="E23" s="9">
+        <f>E9/E3</f>
+        <v>-0.49753694581280777</v>
+      </c>
+      <c r="F23" s="9">
+        <f>F9/F3</f>
+        <v>-0.51231527093596041</v>
+      </c>
       <c r="G23" s="9">
         <f>G9/G3</f>
         <v>-0.55414012738853524</v>
@@ -2631,6 +2889,14 @@
         <f>H9/H3</f>
         <v>-0.49162011173184367</v>
       </c>
+      <c r="I23" s="9">
+        <f>I9/I3</f>
+        <v>-0.54945054945054972</v>
+      </c>
+      <c r="J23" s="9">
+        <f>J9/J3</f>
+        <v>-0.54894736842105274</v>
+      </c>
       <c r="L23" s="9">
         <f>L9/L3</f>
         <v>-0.78320610687022907</v>
@@ -2640,55 +2906,55 @@
         <v>-0.53350854139290427</v>
       </c>
       <c r="N23" s="9">
-        <f t="shared" ref="N23:X23" si="20">N9/N3</f>
-        <v>-0.42111898016997151</v>
+        <f t="shared" ref="N23:X23" si="24">N9/N3</f>
+        <v>-0.53573446327683627</v>
       </c>
       <c r="O23" s="9">
-        <f t="shared" si="20"/>
-        <v>-0.20727743902439014</v>
+        <f t="shared" si="24"/>
+        <v>-0.34280487804878046</v>
       </c>
       <c r="P23" s="9">
-        <f t="shared" si="20"/>
-        <v>-7.7451936872309834E-2</v>
+        <f t="shared" si="24"/>
+        <v>-0.20302008608321373</v>
       </c>
       <c r="Q23" s="9">
-        <f t="shared" si="20"/>
-        <v>9.0562230989958536E-3</v>
+        <f t="shared" si="24"/>
+        <v>-0.10607133249641315</v>
       </c>
       <c r="R23" s="9">
-        <f t="shared" si="20"/>
-        <v>6.8411181850789315E-2</v>
+        <f t="shared" si="24"/>
+        <v>-4.5974077893352387E-2</v>
       </c>
       <c r="S23" s="9">
-        <f t="shared" si="20"/>
-        <v>0.10922666498001656</v>
+        <f t="shared" si="24"/>
+        <v>-4.2103047392736542E-3</v>
       </c>
       <c r="T23" s="9">
-        <f t="shared" si="20"/>
-        <v>0.13550676041699525</v>
+        <f t="shared" si="24"/>
+        <v>2.3179585030248109E-2</v>
       </c>
       <c r="U23" s="9">
-        <f t="shared" si="20"/>
-        <v>0.1549305409048001</v>
+        <f t="shared" si="24"/>
+        <v>4.3789341127809037E-2</v>
       </c>
       <c r="V23" s="9">
-        <f t="shared" si="20"/>
-        <v>0.15685116416100503</v>
+        <f t="shared" si="24"/>
+        <v>4.6389521822088699E-2</v>
       </c>
       <c r="W23" s="9">
-        <f t="shared" si="20"/>
-        <v>0.14831787174590774</v>
+        <f t="shared" si="24"/>
+        <v>3.7951043767159132E-2</v>
       </c>
       <c r="X23" s="9">
-        <f t="shared" si="20"/>
-        <v>0.14831787174590771</v>
+        <f t="shared" si="24"/>
+        <v>3.7951043767159208E-2</v>
       </c>
       <c r="Z23" t="s">
         <v>43</v>
       </c>
       <c r="AA23" s="3">
         <f>AA21+AA22</f>
-        <v>440.72401453576623</v>
+        <v>168.02423317862798</v>
       </c>
     </row>
     <row r="24" spans="2:27" x14ac:dyDescent="0.3">
@@ -2699,6 +2965,18 @@
         <f>C12/C11</f>
         <v>0</v>
       </c>
+      <c r="D24" s="9">
+        <f>D12/D11</f>
+        <v>0</v>
+      </c>
+      <c r="E24" s="9">
+        <f>E12/E11</f>
+        <v>0</v>
+      </c>
+      <c r="F24" s="9">
+        <f>F12/F11</f>
+        <v>0</v>
+      </c>
       <c r="G24" s="9">
         <f>G12/G11</f>
         <v>0</v>
@@ -2707,6 +2985,14 @@
         <f>H12/H11</f>
         <v>0</v>
       </c>
+      <c r="I24" s="9">
+        <f>I12/I11</f>
+        <v>0</v>
+      </c>
+      <c r="J24" s="9">
+        <f>J12/J11</f>
+        <v>0</v>
+      </c>
       <c r="L24" s="9">
         <f>L12/L11</f>
         <v>0</v>
@@ -2716,47 +3002,47 @@
         <v>0</v>
       </c>
       <c r="N24" s="9">
-        <f t="shared" ref="N24:X24" si="21">N12/N11</f>
+        <f t="shared" ref="N24:X24" si="25">N12/N11</f>
+        <v>0</v>
+      </c>
+      <c r="O24" s="9">
+        <f t="shared" si="25"/>
         <v>0.2</v>
       </c>
-      <c r="O24" s="9">
-        <f t="shared" si="21"/>
+      <c r="P24" s="9">
+        <f t="shared" si="25"/>
+        <v>0.20000000000000004</v>
+      </c>
+      <c r="Q24" s="9">
+        <f t="shared" si="25"/>
+        <v>0.19999999999999998</v>
+      </c>
+      <c r="R24" s="9">
+        <f t="shared" si="25"/>
         <v>0.2</v>
       </c>
-      <c r="P24" s="9">
-        <f t="shared" si="21"/>
+      <c r="S24" s="9">
+        <f t="shared" si="25"/>
         <v>0.2</v>
       </c>
-      <c r="Q24" s="9">
-        <f t="shared" si="21"/>
+      <c r="T24" s="9">
+        <f t="shared" si="25"/>
         <v>0.2</v>
       </c>
-      <c r="R24" s="9">
-        <f t="shared" si="21"/>
-        <v>0.19999999999999998</v>
-      </c>
-      <c r="S24" s="9">
-        <f t="shared" si="21"/>
+      <c r="U24" s="9">
+        <f t="shared" si="25"/>
         <v>0.2</v>
       </c>
-      <c r="T24" s="9">
-        <f t="shared" si="21"/>
+      <c r="V24" s="9">
+        <f t="shared" si="25"/>
         <v>0.2</v>
       </c>
-      <c r="U24" s="9">
-        <f t="shared" si="21"/>
+      <c r="W24" s="9">
+        <f t="shared" si="25"/>
         <v>0.2</v>
       </c>
-      <c r="V24" s="9">
-        <f t="shared" si="21"/>
-        <v>0.2</v>
-      </c>
-      <c r="W24" s="9">
-        <f t="shared" si="21"/>
-        <v>0.2</v>
-      </c>
       <c r="X24" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>0.2</v>
       </c>
       <c r="Z24" t="s">
@@ -2764,7 +3050,7 @@
       </c>
       <c r="AA24" s="2">
         <f>AA23/X15</f>
-        <v>24.215605194272872</v>
+        <v>9.1816520862638242</v>
       </c>
     </row>
     <row r="25" spans="2:27" x14ac:dyDescent="0.3">
@@ -2775,6 +3061,18 @@
         <f>C14/C3</f>
         <v>-0.64473684210526327</v>
       </c>
+      <c r="D25" s="9">
+        <f>D14/D3</f>
+        <v>-0.6206896551724137</v>
+      </c>
+      <c r="E25" s="9">
+        <f>E14/E3</f>
+        <v>-0.47783251231527091</v>
+      </c>
+      <c r="F25" s="9">
+        <f>F14/F3</f>
+        <v>-0.50246305418719195</v>
+      </c>
       <c r="G25" s="9">
         <f>G14/G3</f>
         <v>-0.52229299363057347</v>
@@ -2783,6 +3081,14 @@
         <f>H14/H3</f>
         <v>-0.47486033519553078</v>
       </c>
+      <c r="I25" s="9">
+        <f>I14/I3</f>
+        <v>-0.49450549450549475</v>
+      </c>
+      <c r="J25" s="9">
+        <f>J14/J3</f>
+        <v>-0.49631578947368427</v>
+      </c>
       <c r="L25" s="9">
         <f>L14/L3</f>
         <v>-0.7969465648854962</v>
@@ -2792,64 +3098,64 @@
         <v>-0.55584756898817367</v>
       </c>
       <c r="N25" s="9">
-        <f t="shared" ref="N25:X25" si="22">N14/N3</f>
-        <v>-0.29478328611898008</v>
+        <f t="shared" ref="N25:X25" si="26">N14/N3</f>
+        <v>-0.49618644067796625</v>
       </c>
       <c r="O25" s="9">
-        <f t="shared" si="22"/>
-        <v>-0.14509420731707309</v>
+        <f t="shared" si="26"/>
+        <v>-0.23996341463414633</v>
       </c>
       <c r="P25" s="9">
-        <f t="shared" si="22"/>
-        <v>-5.421635581061688E-2</v>
+        <f t="shared" si="26"/>
+        <v>-0.1421140602582496</v>
       </c>
       <c r="Q25" s="9">
-        <f t="shared" si="22"/>
-        <v>6.3393561692970963E-3</v>
+        <f t="shared" si="26"/>
+        <v>-7.4249932747489214E-2</v>
       </c>
       <c r="R25" s="9">
-        <f t="shared" si="22"/>
-        <v>4.7887827295552521E-2</v>
+        <f t="shared" si="26"/>
+        <v>-3.2181854525346679E-2</v>
       </c>
       <c r="S25" s="9">
-        <f t="shared" si="22"/>
-        <v>7.6458665486011587E-2</v>
+        <f t="shared" si="26"/>
+        <v>-2.947213317491558E-3</v>
       </c>
       <c r="T25" s="9">
-        <f t="shared" si="22"/>
-        <v>9.4854732291896671E-2</v>
+        <f t="shared" si="26"/>
+        <v>1.6225709521173675E-2</v>
       </c>
       <c r="U25" s="9">
-        <f t="shared" si="22"/>
-        <v>0.10845137863336006</v>
+        <f t="shared" si="26"/>
+        <v>3.0652538789466326E-2</v>
       </c>
       <c r="V25" s="9">
-        <f t="shared" si="22"/>
-        <v>0.10979581491270352</v>
+        <f t="shared" si="26"/>
+        <v>3.2472665275462095E-2</v>
       </c>
       <c r="W25" s="9">
-        <f t="shared" si="22"/>
-        <v>0.1038225102221354</v>
+        <f t="shared" si="26"/>
+        <v>2.6565730637011387E-2</v>
       </c>
       <c r="X25" s="9">
-        <f t="shared" si="22"/>
-        <v>0.10382251022213539</v>
+        <f t="shared" si="26"/>
+        <v>2.6565730637011446E-2</v>
       </c>
       <c r="Z25" t="s">
         <v>45</v>
       </c>
       <c r="AA25" s="2">
         <f>Main!D3</f>
-        <v>35.03</v>
+        <v>25.87</v>
       </c>
     </row>
     <row r="26" spans="2:27" x14ac:dyDescent="0.3">
       <c r="Z26" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AA26" s="11">
+      <c r="AA26" s="10">
         <f>AA24/AA25-1</f>
-        <v>-0.30871809322658095</v>
+        <v>-0.64508495994341608</v>
       </c>
     </row>
     <row r="27" spans="2:27" x14ac:dyDescent="0.3">
